--- a/التعريفة.xlsx
+++ b/التعريفة.xlsx
@@ -1,17 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\othma\Desktop\Projects\FreeZone\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975A2CB6-AC89-4C57-B46C-3DC379D8428F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="20115" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الحاويات" sheetId="1" r:id="rId1"/>
     <sheet name="البضائع الصب" sheetId="2" r:id="rId2"/>
     <sheet name="ورقة3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -132,12 +151,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -146,7 +165,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -160,7 +179,7 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -500,103 +519,103 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -609,14 +628,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="نسق Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -654,7 +676,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -726,7 +748,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -899,594 +921,594 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="33.125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="7" customWidth="1"/>
-    <col min="3" max="14" width="8.5" style="7" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="33.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="3" customWidth="1"/>
+    <col min="3" max="14" width="8.44140625" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:14" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="6" t="s">
+    <row r="1" spans="1:14" ht="20.25" customHeight="1" thickBot="1"/>
+    <row r="2" spans="1:14" ht="20.25" customHeight="1" thickTop="1">
+      <c r="A2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="3" t="s">
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="3" t="s">
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="5"/>
-    </row>
-    <row r="3" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="8">
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="32"/>
+    </row>
+    <row r="3" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="4">
         <v>38.5</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="5">
         <v>77</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="5">
         <v>86</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="6">
         <v>95</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="7">
         <v>38.5</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="5">
         <v>77</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="5">
         <v>86</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="6">
         <v>95</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="7">
         <v>38.5</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="5">
         <v>77</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="5">
         <v>86</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="6">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="4">
         <v>375</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="5">
         <v>750</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="5">
         <v>750</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="6">
         <v>750</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="7">
         <v>375</v>
       </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9">
+      <c r="H4" s="5"/>
+      <c r="I4" s="5">
         <v>750</v>
       </c>
-      <c r="J4" s="10"/>
-      <c r="K4" s="11">
+      <c r="J4" s="6"/>
+      <c r="K4" s="7">
         <v>125</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="5">
         <v>250</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="5">
         <v>250</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="6">
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A5" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A6" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A7" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="4">
         <v>62.5</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="8">
         <v>125</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="5">
         <v>125</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="6">
         <v>125</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="7">
         <v>125</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="9">
+      <c r="H7" s="8"/>
+      <c r="I7" s="5">
         <v>250</v>
       </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="11">
+      <c r="J7" s="6"/>
+      <c r="K7" s="7">
         <v>31.05</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="8">
         <v>62.5</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="5">
         <v>62.5</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="6">
         <v>62.5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
+    <row r="8" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="4">
         <v>0.25</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="8">
         <v>0.25</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="6">
         <v>0.25</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="7">
         <v>0.25</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="9">
+      <c r="H8" s="8"/>
+      <c r="I8" s="5">
         <v>0.25</v>
       </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="11">
+      <c r="J8" s="6"/>
+      <c r="K8" s="7">
         <v>0.25</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="8">
         <v>0.25</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="5">
         <v>0.25</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="6">
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A9" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="10"/>
-    </row>
-    <row r="10" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="B9" s="19"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A10" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="4">
         <v>96</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="8">
         <v>192.5</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="5">
         <v>215</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="6">
         <v>240</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="7">
         <v>96</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="8">
         <v>192.5</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="5">
         <v>215</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="6">
         <v>2.4</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="7">
         <v>96</v>
       </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="9">
+      <c r="L10" s="8"/>
+      <c r="M10" s="5">
         <v>215</v>
       </c>
-      <c r="N10" s="10"/>
-    </row>
-    <row r="11" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A11" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="4">
         <v>0.38</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="8">
         <v>0.38</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="5">
         <v>0.38</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="6">
         <v>0.38</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="7">
         <v>0.38</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="8">
         <v>0.32</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="5">
         <v>0.38</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="6">
         <v>0.38</v>
       </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="10"/>
-    </row>
-    <row r="12" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
+      <c r="K11" s="7"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A12" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="4">
         <v>0.5</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="8">
         <v>0.5</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="5">
         <v>0.5</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="6">
         <v>0.5</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="7">
         <v>0.5</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="8">
         <v>0.5</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="5">
         <v>0.5</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="6">
         <v>0.5</v>
       </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="10"/>
-    </row>
-    <row r="13" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
+      <c r="K12" s="7"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="4">
         <v>100</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="4">
         <v>100</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="4">
         <v>100</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="4">
         <v>100</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="4">
         <v>100</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="4">
         <v>100</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="4">
         <v>100</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="4">
         <v>100</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="4">
         <v>100</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="4">
         <v>100</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="4">
         <v>100</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A14" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="10"/>
-    </row>
-    <row r="15" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="B14" s="19"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11">
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7">
         <v>100</v>
       </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="10"/>
-    </row>
-    <row r="16" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="10"/>
-    </row>
-    <row r="17" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
+      <c r="B16" s="19"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A17" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
+      <c r="B17" s="19"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A18" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="10"/>
-    </row>
-    <row r="19" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+      <c r="B18" s="19"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A19" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="8">
+      <c r="B19" s="19"/>
+      <c r="C19" s="4">
         <v>2</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="5">
         <v>2</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="5">
         <v>2</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="6">
         <v>2</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="7">
         <v>0.626</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="7">
         <v>0.626</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="7">
         <v>0.626</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="7">
         <v>0.626</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="7">
         <v>6.2E-2</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="7">
         <v>6.2E-2</v>
       </c>
-      <c r="M19" s="11">
+      <c r="M19" s="7">
         <v>6.2E-2</v>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="7">
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
+    <row r="20" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A20" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="8">
+      <c r="B20" s="19"/>
+      <c r="C20" s="4">
         <v>50</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="5">
         <v>50</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="5">
         <v>50</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="6">
         <v>50</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9">
+      <c r="G20" s="7"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5">
         <v>0</v>
       </c>
-      <c r="J20" s="10"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="10"/>
-    </row>
-    <row r="21" spans="1:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+      <c r="J20" s="6"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A21" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="15"/>
-    </row>
-    <row r="22" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" spans="1:14" ht="20.25" customHeight="1">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1500,87 +1522,87 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="19.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.5" style="7" customWidth="1"/>
-    <col min="2" max="2" width="13.75" style="7" customWidth="1"/>
-    <col min="3" max="3" width="9" style="7"/>
-    <col min="4" max="4" width="12.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="7"/>
-    <col min="7" max="7" width="26.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="9" style="7"/>
+    <col min="1" max="1" width="31.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9" style="3"/>
+    <col min="4" max="4" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="3"/>
+    <col min="7" max="7" width="26.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J1" s="32" t="s">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" thickBot="1">
+      <c r="J1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="33"/>
-    </row>
-    <row r="2" spans="1:11" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27" t="s">
+      <c r="K1" s="35"/>
+    </row>
+    <row r="2" spans="1:11" ht="19.5" customHeight="1" thickTop="1">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="35" t="s">
+      <c r="K2" s="29" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+    <row r="3" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="25">
         <v>13</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="25">
         <v>13</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="25">
         <v>13</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="25">
         <v>13</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="25">
         <v>4</v>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="25">
         <v>1.5</v>
       </c>
-      <c r="J3" s="29">
+      <c r="J3" s="25">
         <v>21.5</v>
       </c>
       <c r="K3" s="1">
@@ -1588,55 +1610,55 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+    <row r="4" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
       <c r="K4" s="1">
         <f t="shared" ref="K4:K20" si="0">J4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28" t="s">
+    <row r="5" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A5" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
       <c r="K5" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28" t="s">
+    <row r="6" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29">
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25">
         <v>3.13</v>
       </c>
       <c r="K6" s="1">
@@ -1644,31 +1666,31 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="s">
+    <row r="7" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A7" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="25">
         <v>0.25</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="25">
         <v>0.25</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="25">
         <v>0.25</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="25">
         <v>0.25</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="25">
         <v>0.25</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="25">
         <v>0.25</v>
       </c>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25">
         <v>0.25</v>
       </c>
       <c r="K7" s="1">
@@ -1676,33 +1698,33 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="s">
+    <row r="8" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A8" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="25">
         <v>0.5</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="25">
         <v>0.5</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="25">
         <v>0.5</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="25">
         <v>0.5</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="25">
         <v>0.5</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="25">
         <v>0.5</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="25">
         <v>0.5</v>
       </c>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29">
+      <c r="I8" s="25"/>
+      <c r="J8" s="25">
         <v>0.5</v>
       </c>
       <c r="K8" s="1">
@@ -1710,19 +1732,19 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+    <row r="9" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A9" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29">
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25">
         <v>8</v>
       </c>
       <c r="K9" s="1">
@@ -1730,19 +1752,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="s">
+    <row r="10" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A10" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29">
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25">
         <v>0.38</v>
       </c>
       <c r="K10" s="1">
@@ -1750,19 +1772,19 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28" t="s">
+    <row r="11" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A11" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29">
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25">
         <v>0.5</v>
       </c>
       <c r="K11" s="1">
@@ -1770,92 +1792,92 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28" t="s">
+    <row r="12" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
       <c r="K12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28" t="s">
+    <row r="13" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A13" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29">
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25">
         <v>25</v>
       </c>
       <c r="K13" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28" t="s">
+    <row r="14" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A14" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
       <c r="K14" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28" t="s">
+    <row r="15" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A15" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
       <c r="K15" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+    <row r="16" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A16" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29">
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25">
         <v>1.25</v>
       </c>
       <c r="K16" s="1">
@@ -1863,51 +1885,51 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28" t="s">
+    <row r="17" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A17" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
       <c r="K17" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28" t="s">
+    <row r="18" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A18" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="25">
         <v>2</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="25">
         <v>2</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="25">
         <v>2</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="25">
         <v>2</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="25">
         <v>2</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="25">
         <v>2</v>
       </c>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29">
+      <c r="H18" s="25"/>
+      <c r="I18" s="25">
         <v>2</v>
       </c>
-      <c r="J18" s="29">
+      <c r="J18" s="25">
         <v>2</v>
       </c>
       <c r="K18" s="1">
@@ -1915,44 +1937,44 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28" t="s">
+    <row r="19" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A19" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
       <c r="K19" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
+    <row r="20" spans="1:11" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A20" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
       <c r="K20" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
+    <row r="21" spans="1:11" ht="19.5" customHeight="1" thickTop="1">
+      <c r="A21" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1964,9 +1986,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
